--- a/102401322/output/xlsx/大语言模型弹幕分析统计.xlsx
+++ b/102401322/output/xlsx/大语言模型弹幕分析统计.xlsx
@@ -659,8 +659,10 @@
       <c r="C2" t="n">
         <v>26569</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.4316</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>43.2%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -675,8 +677,10 @@
       <c r="C3" t="n">
         <v>20210</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.3283</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>32.8%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -691,8 +695,10 @@
       <c r="C4" t="n">
         <v>14777</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.2401</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -19993,8 +19999,10 @@
       <c r="C2" t="n">
         <v>2009</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.3722</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>37.2%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -20009,8 +20017,10 @@
       <c r="C3" t="n">
         <v>622</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.1152</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -20025,8 +20035,10 @@
       <c r="C4" t="n">
         <v>522</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.09669999999999999</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -20041,8 +20053,10 @@
       <c r="C5" t="n">
         <v>505</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.0936</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9.4%</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -20057,8 +20071,10 @@
       <c r="C6" t="n">
         <v>500</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0926</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9.3%</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -20073,8 +20089,10 @@
       <c r="C7" t="n">
         <v>470</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.0871</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.7%</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -20089,8 +20107,10 @@
       <c r="C8" t="n">
         <v>366</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.0678</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -20105,8 +20125,10 @@
       <c r="C9" t="n">
         <v>291</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0539</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -20121,8 +20143,10 @@
       <c r="C10" t="n">
         <v>112</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.0208</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20319,8 +20343,10 @@
       <c r="C2" t="n">
         <v>479</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.2868</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>28.7%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -20335,8 +20361,10 @@
       <c r="C3" t="n">
         <v>304</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.182</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -20351,8 +20379,10 @@
       <c r="C4" t="n">
         <v>235</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.1407</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>14.1%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -20367,8 +20397,10 @@
       <c r="C5" t="n">
         <v>204</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.1222</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12.2%</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -20383,8 +20415,10 @@
       <c r="C6" t="n">
         <v>119</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0713</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -20399,8 +20433,10 @@
       <c r="C7" t="n">
         <v>79</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.0473</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -20415,8 +20451,10 @@
       <c r="C8" t="n">
         <v>74</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.0443</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -20431,8 +20469,10 @@
       <c r="C9" t="n">
         <v>42</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0251</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21827,8 +21867,10 @@
       <c r="C2" t="n">
         <v>1313</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.6709000000000001</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>67.1%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -21843,8 +21885,10 @@
       <c r="C3" t="n">
         <v>400</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.2044</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -21859,8 +21903,10 @@
       <c r="C4" t="n">
         <v>244</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.1247</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21917,8 +21963,10 @@
       <c r="C2" t="n">
         <v>600</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.5124</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51.2%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -21933,8 +21981,10 @@
       <c r="C3" t="n">
         <v>265</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.2263</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22.6%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -21949,8 +21999,10 @@
       <c r="C4" t="n">
         <v>165</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.1409</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>14.1%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -21965,8 +22017,10 @@
       <c r="C5" t="n">
         <v>78</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.06660000000000001</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -21981,8 +22035,10 @@
       <c r="C6" t="n">
         <v>63</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0538</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22039,8 +22095,10 @@
       <c r="C2" t="n">
         <v>78</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.2921</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -22055,8 +22113,10 @@
       <c r="C3" t="n">
         <v>78</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.2921</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -22071,8 +22131,10 @@
       <c r="C4" t="n">
         <v>67</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.2509</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>25.1%</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -22087,8 +22149,10 @@
       <c r="C5" t="n">
         <v>26</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.0974</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -22103,8 +22167,10 @@
       <c r="C6" t="n">
         <v>18</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0674</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
       </c>
     </row>
   </sheetData>
